--- a/results/02_taxa_assemblage/WardsClustering/tables/reference_taxa_clusters.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/reference_taxa_clusters.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>0.8019817499587525</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>2.010888316142736</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>3.203426503814917e-16</v>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>1.611075341040287</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>1.150242635580613</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>1.529467388129453</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>0.399421886369236</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>3.203426503814917e-16</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>0.3263154121283017</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
         <v>0.8654578766211725</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>1.304854581528421</v>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
         <v>3.203426503814917e-16</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>3.203426503814917e-16</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
         <v>3.203426503814917e-16</v>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
         <v>0.5574817642990493</v>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
         <v>2.813555626621104</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
         <v>3.203426503814917e-16</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
         <v>1.330645311988472</v>
